--- a/Pathologie Infectieuse/data/Annale 3.xlsx
+++ b/Pathologie Infectieuse/data/Annale 3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moito\Desktop\Sérieux\Projet\Site web\Pathologie Infectieuse\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ABB0D36-0D9A-4A82-B880-02ECCE0E763F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4F4E59-6252-41D1-B690-DFE902023FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{657BDCD0-33AC-429E-9C10-5C3E27D80627}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{657BDCD0-33AC-429E-9C10-5C3E27D80627}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2013,7 +2013,7 @@
         <v>19</v>
       </c>
       <c r="D14" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" t="s">
         <v>260</v>
@@ -2133,7 +2133,7 @@
         <v>26</v>
       </c>
       <c r="D20" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="s">
         <v>266</v>
@@ -2373,7 +2373,7 @@
         <v>41</v>
       </c>
       <c r="D32" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="s">
         <v>278</v>
@@ -2653,7 +2653,7 @@
         <v>57</v>
       </c>
       <c r="D46" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="s">
         <v>292</v>
@@ -3638,7 +3638,7 @@
         <v>117</v>
       </c>
       <c r="D96" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="s">
         <v>337</v>
@@ -4058,7 +4058,7 @@
         <v>143</v>
       </c>
       <c r="D117" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E117" t="s">
         <v>358</v>
@@ -4098,7 +4098,7 @@
         <v>145</v>
       </c>
       <c r="D119" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="s">
         <v>360</v>
@@ -4118,7 +4118,7 @@
         <v>146</v>
       </c>
       <c r="D120" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="s">
         <v>361</v>
@@ -4138,7 +4138,7 @@
         <v>147</v>
       </c>
       <c r="D121" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="s">
         <v>362</v>
@@ -5163,7 +5163,7 @@
         <v>210</v>
       </c>
       <c r="D173" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="s">
         <v>409</v>
